--- a/artfynd/A 48972-2025 artfynd.xlsx
+++ b/artfynd/A 48972-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>97211163</v>
+        <v>97208624</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>340912.7839363434</v>
+        <v>340911</v>
       </c>
       <c r="R2" t="n">
-        <v>6561353.547462864</v>
+        <v>6561337</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -749,7 +744,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>AE16FA4D-2FFF-45C0-B59B-F84B512724FB</t>
+          <t>260BC84B-0B5A-4593-B7CA-595966D86F60</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -757,24 +752,14 @@
           <t>2017-11-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2017-11-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>{659012B3-75B6-4E41-AC62-F696FE680D9B}</t>
+          <t>{792E3721-BF19-4784-9186-6D7A05583289}</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,6 +783,236 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>97211163</v>
+      </c>
+      <c r="B3" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>BENGTSFORS, Dls</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>340913</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6561354</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>AE16FA4D-2FFF-45C0-B59B-F84B512724FB</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2017-11-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2017-11-09</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>{659012B3-75B6-4E41-AC62-F696FE680D9B}</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Trädportalen</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>97214735</v>
+      </c>
+      <c r="B4" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>BENGTSFORS, Dls</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>340877</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6561292</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vårvik</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>8425271F-8FDC-42C7-9386-DA36B1C84D9C</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2017-11-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2017-11-09</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>{89D084DF-B069-4B49-A717-D563091697F7}</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anna Stenström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Sundh</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
         <is>
           <t>Trädportalen</t>
         </is>

--- a/artfynd/A 48972-2025 artfynd.xlsx
+++ b/artfynd/A 48972-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97208624</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97211163</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1017,8 +1032,18 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97214735</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>